--- a/models/Three_Statement_Model_AI_Palantir.xlsx
+++ b/models/Three_Statement_Model_AI_Palantir.xlsx
@@ -1068,7 +1068,7 @@
     <t xml:space="preserve">Rule of 40 (growth + FCF margin)</t>
   </si>
   <si>
-    <t xml:space="preserve">Rule of 40 at ~103% vs a ~34% median is elite; almost no public software company clears 100%.</t>
+    <t xml:space="preserve">Rule of 40 at ~103% vs a ~34% median — almost no public software company clears 100%.</t>
   </si>
   <si>
     <t xml:space="preserve">EV / Revenue (TTM) (x)</t>

--- a/models/Three_Statement_Model_AI_Palantir.xlsx
+++ b/models/Three_Statement_Model_AI_Palantir.xlsx
@@ -31,12 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="459">
   <si>
     <t xml:space="preserve">PALANTIR TECHNOLOGIES INC.  (NASDAQ: PLTR)</t>
   </si>
   <si>
-    <t xml:space="preserve">Three-Statement Financial Model — AI &amp; Data Analytics Software</t>
+    <t xml:space="preserve">Three-Statement Financial Model · AI &amp; Data Analytics Software</t>
   </si>
   <si>
     <t xml:space="preserve">Integrated Income Statement · Balance Sheet · Cash Flow · driver-based forecast · regional scenarios · live market data</t>
@@ -63,16 +63,16 @@
     <t xml:space="preserve">HOW TO USE THIS MODEL</t>
   </si>
   <si>
-    <t xml:space="preserve">1.  Start on the Revenue Drivers and Assumptions tabs — every blue cell is an input; yellow cells are the key levers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.  Flip the scenario selector on Regional Breakdown (1 = Standard · 2 = Best Case · 3 = Low Case) — the whole model re-runs, including EPS, cash and the benchmarking tab.</t>
+    <t xml:space="preserve">1.  Start on the Revenue Drivers and Assumptions tabs; every blue cell is an input; yellow cells are the key levers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.  Flip the scenario selector on Regional Breakdown (1 = Standard · 2 = Best Case · 3 = Low Case); the whole model re-runs, including EPS, cash and the benchmarking tab.</t>
   </si>
   <si>
     <t xml:space="preserve">3.  Check Budget vs Actual for FY2025 performance vs guidance; rows over the 10% threshold flag automatically.</t>
   </si>
   <si>
-    <t xml:space="preserve">4.  Keep market data current: run refresh_market_data.py in this folder (or use the dashboard ⟳ button) — stamps update on Market Inputs and the refresh is logged in Version History.</t>
+    <t xml:space="preserve">4.  Keep market data current: run refresh_market_data.py in this folder (or use the dashboard ⟳ button); stamps update on Market Inputs and the refresh is logged in Version History.</t>
   </si>
   <si>
     <t xml:space="preserve">5.  For a browser walkthrough or a one-page memo, open Finance_AI_Dashboard.html and use Export memo (PDF).</t>
@@ -84,7 +84,7 @@
     <t xml:space="preserve">•  FY2023–FY2025 as reported in SEC filings; historical statements tie to reported totals. FY2026E revenue growth (60.5%) anchors to management guidance of $7.18–7.20bn.</t>
   </si>
   <si>
-    <t xml:space="preserve">•  Forecast driven entirely by the Revenue Drivers, Assumptions and Regional Breakdown tabs — no hardcodes on statement tabs after FY2025.</t>
+    <t xml:space="preserve">•  Forecast driven entirely by the Revenue Drivers, Assumptions and Regional Breakdown tabs; no hardcodes on statement tabs after FY2025.</t>
   </si>
   <si>
     <t xml:space="preserve">•  Interest income accrues on beginning-of-year balances (no circular references); balance sheet balances in all periods under every scenario.</t>
@@ -93,19 +93,19 @@
     <t xml:space="preserve">COLOR CONVENTIONS</t>
   </si>
   <si>
-    <t xml:space="preserve">Blue — hardcoded input (historical figures as reported; forecast assumptions)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black — formula / calculation          Green — direct link to another sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellow fill — key assumption levers to flex</t>
+    <t xml:space="preserve">Blue = hardcoded input (historical figures as reported; forecast assumptions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black = formula / calculation          Green = direct link to another sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yellow fill = key assumption levers to flex</t>
   </si>
   <si>
     <t xml:space="preserve">Every data input is cited on the Sources tab, with links and last-updated dates.</t>
   </si>
   <si>
-    <t xml:space="preserve">Palantir Technologies Inc. — Forecast Assumptions</t>
+    <t xml:space="preserve">Palantir Technologies Inc.; Forecast Assumptions</t>
   </si>
   <si>
     <t xml:space="preserve">(USD in thousands, except per-share amounts) · FY2023A–FY2025A per SEC filings · FY2026E–FY2030E forecast</t>
@@ -138,13 +138,13 @@
     <t xml:space="preserve">Income statement drivers</t>
   </si>
   <si>
-    <t xml:space="preserve">    Revenue growth % — OUTPUT (driven by Revenue Drivers tab)</t>
+    <t xml:space="preserve">    Revenue growth % · OUTPUT (driven by Revenue Drivers tab)</t>
   </si>
   <si>
     <t xml:space="preserve">FY26E ≈ company guidance of $7.18–7.20bn (+61% y/y); growth tapers as base scales</t>
   </si>
   <si>
-    <t xml:space="preserve">    Gross margin % — OUTPUT (driven by Revenue Drivers tab)</t>
+    <t xml:space="preserve">    Gross margin % · OUTPUT (driven by Revenue Drivers tab)</t>
   </si>
   <si>
     <t xml:space="preserve">Software gross margin with modest AI-compute drag offset by scale</t>
@@ -189,7 +189,7 @@
     <t xml:space="preserve">Balance sheet drivers</t>
   </si>
   <si>
-    <t xml:space="preserve">    Accounts receivable — days sales outstanding</t>
+    <t xml:space="preserve">    Accounts receivable · days sales outstanding</t>
   </si>
   <si>
     <t xml:space="preserve">Large government/strategic contracts lengthen collections</t>
@@ -240,7 +240,7 @@
     <t xml:space="preserve">Marketable securities, lease balances and noncontrolling interests held flat in the forecast for simplicity.</t>
   </si>
   <si>
-    <t xml:space="preserve">Palantir Technologies Inc. — Revenue Drivers (AI)</t>
+    <t xml:space="preserve">Palantir Technologies Inc.; Revenue Drivers (AI)</t>
   </si>
   <si>
     <t xml:space="preserve">Bottoms-up AI revenue &amp; compute-cost build (USD in thousands unless noted) · drives Revenue and Cost of revenue on the Income Statement</t>
@@ -255,7 +255,7 @@
     <t xml:space="preserve">        Government revenue growth %</t>
   </si>
   <si>
-    <t xml:space="preserve">Commercial segment — enterprise contracts</t>
+    <t xml:space="preserve">Commercial segment · enterprise contracts</t>
   </si>
   <si>
     <t xml:space="preserve">    Commercial customers (end of period)</t>
@@ -276,22 +276,22 @@
     <t xml:space="preserve">AIP subscription tiers (illustrative self-serve ramp from FY2026E)</t>
   </si>
   <si>
-    <t xml:space="preserve">    Starter tier — customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Starter tier — annual price ($000s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Professional tier — customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Professional tier — annual price ($000s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Enterprise AIP tier — customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Enterprise AIP tier — annual price ($000s)</t>
+    <t xml:space="preserve">    Starter tier · customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Starter tier · annual price ($000s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Professional tier · customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Professional tier · annual price ($000s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Enterprise AIP tier · customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Enterprise AIP tier · annual price ($000s)</t>
   </si>
   <si>
     <t xml:space="preserve">    Subscription tier revenue ($000s)</t>
@@ -333,13 +333,13 @@
     <t xml:space="preserve">Government / commercial splits and customer counts per company disclosures (10-Ks, Q4 FY2025 investor presentation).</t>
   </si>
   <si>
-    <t xml:space="preserve">Palantir does not disclose query volumes or unit compute costs — the compute block is an illustrative unit-economics frame (inputs in blue).</t>
+    <t xml:space="preserve">Palantir does not disclose query volumes or unit compute costs; the compute block is an illustrative unit-economics frame (inputs in blue).</t>
   </si>
   <si>
     <t xml:space="preserve">Subscription tiers model an illustrative AIP self-serve ramp; set tier customer counts to zero to remove.</t>
   </si>
   <si>
-    <t xml:space="preserve">Palantir Technologies Inc. — Regional Breakdown &amp; Scenarios</t>
+    <t xml:space="preserve">Palantir Technologies Inc.; Regional Breakdown &amp; Scenarios</t>
   </si>
   <si>
     <t xml:space="preserve">Revenue, growth and customers by region (USD in thousands unless noted) · regional scenario toggle feeds the Income Statement · base = total revenue</t>
@@ -369,16 +369,16 @@
     <t xml:space="preserve">    Base total revenue before regional split</t>
   </si>
   <si>
-    <t xml:space="preserve">    North America — base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Europe — base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Asia Pacific — base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Other / rest of world — base</t>
+    <t xml:space="preserve">    North America · base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Europe · base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Asia Pacific · base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Other / rest of world · base</t>
   </si>
   <si>
     <t xml:space="preserve">    Total base (sum of regions)</t>
@@ -399,40 +399,40 @@
     <t xml:space="preserve">SCENARIO GROWTH DELTAS (added to base regional growth)</t>
   </si>
   <si>
-    <t xml:space="preserve">    Best Case — North America</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Best Case — Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Best Case — Asia Pacific</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Low Case — North America</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Low Case — Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Low Case — Asia Pacific</t>
+    <t xml:space="preserve">    Best Case · North America</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Best Case · Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Best Case · Asia Pacific</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Low Case · North America</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Low Case · Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Low Case · Asia Pacific</t>
   </si>
   <si>
     <t xml:space="preserve">SCENARIO TOTAL REVENUE BY REGION ($000s)</t>
   </si>
   <si>
-    <t xml:space="preserve">    North America — scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Europe — scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Asia Pacific — scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Other / rest of world — scenario (no delta)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL — SCENARIO ($000s)</t>
+    <t xml:space="preserve">    North America · scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Europe · scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Asia Pacific · scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Other / rest of world · scenario (no delta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL · SCENARIO ($000s)</t>
   </si>
   <si>
     <t xml:space="preserve">    Scenario total growth %</t>
@@ -447,13 +447,13 @@
     <t xml:space="preserve">SCENARIO IMPACT DASHBOARD (flips with the selector)</t>
   </si>
   <si>
-    <t xml:space="preserve">    Net income — scenario ($000s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Diluted EPS — scenario ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Ending cash — scenario ($000s)</t>
+    <t xml:space="preserve">    Net income · scenario ($000s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Diluted EPS · scenario ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Ending cash · scenario ($000s)</t>
   </si>
   <si>
     <t xml:space="preserve">    Revenue CAGR FY2025A → FY2030E (scenario)</t>
@@ -480,16 +480,16 @@
     <t xml:space="preserve">    Other customer mix % (balancing)</t>
   </si>
   <si>
-    <t xml:space="preserve">    North America — customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Europe — customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Asia Pacific — customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Other — customers</t>
+    <t xml:space="preserve">    North America · customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Europe · customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Asia Pacific · customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Other · customers</t>
   </si>
   <si>
     <t xml:space="preserve">Check: regional mix sums to 100% (must be 0)</t>
@@ -504,10 +504,10 @@
     <t xml:space="preserve">•  Scenario deltas add to each region's base growth and compound; "Other" carries no delta. The scenario total feeds Revenue on the Income Statement, so every downstream statement, the variance tab and the valuation cross-check flex with the toggle.</t>
   </si>
   <si>
-    <t xml:space="preserve">•  Customer regional mix is an estimate — Palantir disclosed 954 total customers at FY25 but not their geography.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palantir Technologies Inc. — Income Statement</t>
+    <t xml:space="preserve">•  Customer regional mix is an estimate; Palantir disclosed 954 total customers at FY25 but not their geography.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palantir Technologies Inc.; Income Statement</t>
   </si>
   <si>
     <t xml:space="preserve">Revenue</t>
@@ -573,7 +573,7 @@
     <t xml:space="preserve">Memo: depreciation and amortization</t>
   </si>
   <si>
-    <t xml:space="preserve">Palantir Technologies Inc. — Balance Sheet</t>
+    <t xml:space="preserve">Palantir Technologies Inc.; Balance Sheet</t>
   </si>
   <si>
     <t xml:space="preserve">Assets</t>
@@ -678,7 +678,7 @@
     <t xml:space="preserve">Must be zero in every period</t>
   </si>
   <si>
-    <t xml:space="preserve">Palantir Technologies Inc. — Statement of Cash Flows</t>
+    <t xml:space="preserve">Palantir Technologies Inc.; Statement of Cash Flows</t>
   </si>
   <si>
     <t xml:space="preserve">Operating activities</t>
@@ -759,10 +759,10 @@
     <t xml:space="preserve">Net increase (decrease) in cash</t>
   </si>
   <si>
-    <t xml:space="preserve">    Cash, equivalents and restricted cash — beginning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash, equivalents and restricted cash — ending</t>
+    <t xml:space="preserve">    Cash, equivalents and restricted cash, beginning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash, equivalents and restricted cash, ending</t>
   </si>
   <si>
     <t xml:space="preserve">    Less: restricted cash</t>
@@ -774,7 +774,7 @@
     <t xml:space="preserve">Links to cash on the balance sheet</t>
   </si>
   <si>
-    <t xml:space="preserve">Palantir Technologies Inc. — Budget vs Actual Variance</t>
+    <t xml:space="preserve">Palantir Technologies Inc.; Budget vs Actual Variance</t>
   </si>
   <si>
     <t xml:space="preserve">FY2025 actual vs FY2025 budget (USD in thousands, except per-share) · Budget seeded from company guidance where published; all budget cells editable</t>
@@ -813,7 +813,7 @@
     <t xml:space="preserve">Company FY25 guidance (Feb 3, 2025): $3,741–3,757M</t>
   </si>
   <si>
-    <t xml:space="preserve">Placeholder — replace with your budget</t>
+    <t xml:space="preserve">Placeholder · replace with your budget</t>
   </si>
   <si>
     <t xml:space="preserve">Income from operations (GAAP)</t>
@@ -846,7 +846,7 @@
     <t xml:space="preserve">•  Budget column is seeded with the midpoint of company guidance issued at the start of FY2025 where published (see Budget source).</t>
   </si>
   <si>
-    <t xml:space="preserve">•  Rows marked "Placeholder" carry illustrative budgets — overwrite them, or type your own number in the yellow Override column (it takes precedence).</t>
+    <t xml:space="preserve">•  Rows marked "Placeholder" carry illustrative budgets; overwrite them, or type your own number in the yellow Override column (it takes precedence).</t>
   </si>
   <si>
     <t xml:space="preserve">•  GAAP actuals pull live from the statement tabs (green); non-GAAP actuals are per the company's Q4 FY2025 earnings release.</t>
@@ -855,10 +855,10 @@
     <t xml:space="preserve">•  Rows turn red automatically when |Variance %| exceeds the threshold in B4.</t>
   </si>
   <si>
-    <t xml:space="preserve">Palantir Technologies Inc. — Market Inputs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snapshot as of market close July 17, 2026 · All values are inputs (blue) — see REFRESH section to wire live updates</t>
+    <t xml:space="preserve">Palantir Technologies Inc.; Market Inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snapshot as of market close July 17, 2026 · All values are inputs (blue); see REFRESH section to wire live updates</t>
   </si>
   <si>
     <t xml:space="preserve">Data as of:</t>
@@ -906,7 +906,7 @@
     <t xml:space="preserve">30-year Treasury</t>
   </si>
   <si>
-    <t xml:space="preserve">EQUITY MARKET DATA — PEER SET</t>
+    <t xml:space="preserve">EQUITY MARKET DATA: PEER SET</t>
   </si>
   <si>
     <t xml:space="preserve">PLTR</t>
@@ -945,7 +945,7 @@
     <t xml:space="preserve">Selected EV / Revenue multiple (x)</t>
   </si>
   <si>
-    <t xml:space="preserve">Defaults to this company's current multiple — flex it or use a peer's</t>
+    <t xml:space="preserve">Defaults to this company's current multiple; flex it or use a peer's</t>
   </si>
   <si>
     <t xml:space="preserve">Model FY2026E revenue ($000s)</t>
@@ -975,7 +975,7 @@
     <t xml:space="preserve">Implied premium / (discount) to current market cap</t>
   </si>
   <si>
-    <t xml:space="preserve">REFRESH — MAKE THIS TAB LIVE (one-time setup, ~2 minutes in Excel)</t>
+    <t xml:space="preserve">REFRESH: MAKE THIS TAB LIVE (one-time setup, ~2 minutes in Excel)</t>
   </si>
   <si>
     <t xml:space="preserve">1.  Excel ▸ Data ▸ Get Data (Power Query) ▸ From Other Sources ▸ From Web.</t>
@@ -987,19 +987,19 @@
     <t xml:space="preserve">3.  Load the query to a new sheet; point the blue rate cells above at the latest row (e.g. =INDEX(...)).</t>
   </si>
   <si>
-    <t xml:space="preserve">4.  Share prices (JSON):  https://query1.finance.yahoo.com/v8/finance/chart/PLTR   — Power Query ▸ From Web, drill to chart.result.meta.regularMarketPrice.</t>
+    <t xml:space="preserve">4.  Share prices (JSON):  https://query1.finance.yahoo.com/v8/finance/chart/PLTR  ; Power Query ▸ From Web, drill to chart.result.meta.regularMarketPrice.</t>
   </si>
   <si>
     <t xml:space="preserve">5.  After setup, Data ▸ Refresh All re-pulls everything with one click.</t>
   </si>
   <si>
-    <t xml:space="preserve">6.  Until then this tab is a dated snapshot (see B4) — or ask Claude to refresh the numbers any time.</t>
+    <t xml:space="preserve">6.  Until then this tab is a dated snapshot (see B4); or ask Claude to refresh the numbers any time.</t>
   </si>
   <si>
     <t xml:space="preserve">Sources for this snapshot: Fed H.15 (Jul 17, 2026), NY Fed SOFR, stockanalysis.com / S&amp;P Global (Jul 17–19, 2026).</t>
   </si>
   <si>
-    <t xml:space="preserve">Palantir Technologies Inc. — Competitor Benchmarking</t>
+    <t xml:space="preserve">Palantir Technologies Inc.; Competitor Benchmarking</t>
   </si>
   <si>
     <t xml:space="preserve">Company column pulls live from this model (FY2025 actuals; FY2026E is scenario-aware) · comps per latest reported fiscal year, valuations as of July 17–20, 2026 · industry benchmarks: Clouded Judgement SaaS medians (7/10/26) and US bank norms</t>
@@ -1029,16 +1029,16 @@
     <t xml:space="preserve">—</t>
   </si>
   <si>
-    <t xml:space="preserve">Palantir is now in the same revenue class as Snowflake — with a materially better P&amp;L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue growth — FY2025 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56% growth is ~2x the fastest data-platform comps and ~4x the SaaS median — the core justification for the outlier multiple.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue growth — FY2026E (model, scenario-aware) %</t>
+    <t xml:space="preserve">Palantir is now in the same revenue class as Snowflake, with a materially better P&amp;L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue growth · FY2025 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56% growth is ~2x the fastest data-platform comps and ~4x the SaaS median; the core justification for the outlier multiple.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue growth · FY2026E (model, scenario-aware) %</t>
   </si>
   <si>
     <t xml:space="preserve">n/a</t>
@@ -1047,19 +1047,19 @@
     <t xml:space="preserve">Model FY26E growth (scenario-aware) tracks management guidance of +61%; comps consensus sits in the mid-20s.</t>
   </si>
   <si>
-    <t xml:space="preserve">GAAP gross margin — FY2025 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Above the 76% SaaS median and both comps even while absorbing AI compute — see the compute block on Revenue Drivers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAAP operating margin — FY2025 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAAP-profitable at a 32% margin while SNOW (-31%) and DDOG (-1%) are at or below GAAP breakeven — rare at this growth rate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free cash flow margin — FY2025 %</t>
+    <t xml:space="preserve">GAAP gross margin · FY2025 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Above the 76% SaaS median and both comps even while absorbing AI compute; see the compute block on Revenue Drivers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAAP operating margin · FY2025 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAAP-profitable at a 32% margin while SNOW (-31%) and DDOG (-1%) are at or below GAAP breakeven; rare at this growth rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free cash flow margin · FY2025 %</t>
   </si>
   <si>
     <t xml:space="preserve">47% GAAP FCF margin more than doubles the comps and the 21% median.</t>
@@ -1068,13 +1068,13 @@
     <t xml:space="preserve">Rule of 40 (growth + FCF margin)</t>
   </si>
   <si>
-    <t xml:space="preserve">Rule of 40 at ~103% vs a ~34% median — almost no public software company clears 100%.</t>
+    <t xml:space="preserve">Rule of 40 at ~103% vs a ~34% median; almost no public software company clears 100%.</t>
   </si>
   <si>
     <t xml:space="preserve">EV / Revenue (TTM) (x)</t>
   </si>
   <si>
-    <t xml:space="preserve">59x TTM revenue is ~3x even the high-growth bucket median (20.3x) — the valuation cross-check on Market Inputs shows the beats needed to grow into it.</t>
+    <t xml:space="preserve">59x TTM revenue is ~3x even the high-growth bucket median (20.3x); the valuation cross-check on Market Inputs shows the beats needed to grow into it.</t>
   </si>
   <si>
     <t xml:space="preserve">Forward P/E (x, non-GAAP consensus basis)</t>
@@ -1083,7 +1083,7 @@
     <t xml:space="preserve">~21x S&amp;P 500</t>
   </si>
   <si>
-    <t xml:space="preserve">Cheaper per dollar of forward earnings than SNOW/DDOG, but ~4x the S&amp;P — priced for sustained hypergrowth.</t>
+    <t xml:space="preserve">Cheaper per dollar of forward earnings than SNOW/DDOG, but ~4x the S&amp;P; priced for sustained hypergrowth.</t>
   </si>
   <si>
     <t xml:space="preserve">INDUSTRY BENCHMARK NOTES</t>
@@ -1095,13 +1095,13 @@
     <t xml:space="preserve">•  Rule of 40 = revenue growth % + FCF margin % ≥ 40% is the standard bar for a healthy software business.</t>
   </si>
   <si>
-    <t xml:space="preserve">TAKEAWAYS — WHAT THIS COMPARISON MEANS</t>
+    <t xml:space="preserve">TAKEAWAYS: WHAT THIS COMPARISON MEANS</t>
   </si>
   <si>
     <t xml:space="preserve">•  Palantir screens as the highest-quality operator in the peer set: fastest growth, best GAAP margins, and a Rule of 40 (~103%) roughly 3x the industry median.</t>
   </si>
   <si>
-    <t xml:space="preserve">•  The debate is entirely valuation: at ~59x TTM revenue vs a 20.3x high-growth bucket median, the stock discounts years of continued 40%+ growth — stress this with the Low Case regional scenario.</t>
+    <t xml:space="preserve">•  The debate is entirely valuation: at ~59x TTM revenue vs a 20.3x high-growth bucket median, the stock discounts years of continued 40%+ growth; stress this with the Low Case regional scenario.</t>
   </si>
   <si>
     <t xml:space="preserve">•  Versus SNOW and DDOG, Palantir converts growth to profit far more efficiently; versus the market, its multiple leaves no room for a growth stumble.</t>
@@ -1110,7 +1110,7 @@
     <t xml:space="preserve">Sources: company Q4/FY earnings releases and 10-Ks (SEC EDGAR); stockanalysis.com / S&amp;P Global valuations Jul 17–20, 2026; cloudedjudgement.substack.com 7/10/26; multiples.vc Jul 2026. Comp forward P/Es are consensus (non-GAAP) based.</t>
   </si>
   <si>
-    <t xml:space="preserve">Palantir Technologies Inc. — Version History</t>
+    <t xml:space="preserve">Palantir Technologies Inc.; Version History</t>
   </si>
   <si>
     <t xml:space="preserve">Log of every assumptions refresh: what changed, when, and why. Add a new row each time inputs are updated.</t>
@@ -1143,7 +1143,7 @@
     <t xml:space="preserve">Initial build: FY2023–FY2025 actuals per SEC filings; FY2026–FY2030 top-down forecast; Assumptions, Income Statement, Balance Sheet, Cash Flow and Cover with sheet links.</t>
   </si>
   <si>
-    <t xml:space="preserve">Portfolio work sample — integrated three-statement model with balance and cash tie-out checks.</t>
+    <t xml:space="preserve">Portfolio work sample: integrated three-statement model with balance and cash tie-out checks.</t>
   </si>
   <si>
     <t xml:space="preserve">1.1</t>
@@ -1164,7 +1164,7 @@
     <t xml:space="preserve">Rebuilt revenue as a bottoms-up Revenue Drivers tab (government growth, commercial customers × contract value, AIP tiers, compute cost per query); superseded top-down assumption rows relabeled as OUTPUT.</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit-economics realism — forecast driven by operating metrics rather than a single growth rate.</t>
+    <t xml:space="preserve">Unit-economics realism: forecast driven by operating metrics rather than a single growth rate.</t>
   </si>
   <si>
     <t xml:space="preserve">1.3</t>
@@ -1182,7 +1182,7 @@
     <t xml:space="preserve">Added Competitor Benchmarking tab vs Snowflake and Datadog + SaaS industry medians; company column pulls live from the model with interpretation and takeaways.</t>
   </si>
   <si>
-    <t xml:space="preserve">Relative context — absolute metrics only matter versus peers and industry medians.</t>
+    <t xml:space="preserve">Relative context: absolute metrics only matter versus peers and industry medians.</t>
   </si>
   <si>
     <t xml:space="preserve">1.5</t>
@@ -1200,7 +1200,7 @@
     <t xml:space="preserve">Added this Version History tab.</t>
   </si>
   <si>
-    <t xml:space="preserve">Change auditability — every future assumptions refresh gets logged here.</t>
+    <t xml:space="preserve">Change auditability: every future assumptions refresh gets logged here.</t>
   </si>
   <si>
     <t xml:space="preserve">1.7</t>
@@ -1218,13 +1218,22 @@
     <t xml:space="preserve">Applied workbook protection: all formulas, labels and structure locked with a password on every tab; blue/yellow input cells (assumptions, scenario selector, budget overrides) remain editable so the model stays interactive.</t>
   </si>
   <si>
-    <t xml:space="preserve">Distribution protection — models are downloadable from the public portfolio site; viewers can flex inputs but cannot alter or break the model.</t>
+    <t xml:space="preserve">Distribution protection: models are downloadable from the public portfolio site; viewers can flex inputs but cannot alter or break the model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy edit across all tabs: punctuation and separator cleanup for a natural reading style; no numbers or formulas changed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Readability pass ahead of public distribution.</t>
   </si>
   <si>
     <t xml:space="preserve">How to log a refresh: add a row (yellow cells above are ready) with the new version number, date, your name, the cells/tabs you changed (e.g. "Assumptions F7: FY27 revenue growth 45% → 40% after Q1 FY27 print"), and the reason. Keep one row per refresh so the audit trail stays readable.</t>
   </si>
   <si>
-    <t xml:space="preserve">Palantir Technologies Inc. — Data Sources &amp; Citations</t>
+    <t xml:space="preserve">Palantir Technologies Inc.; Data Sources &amp; Citations</t>
   </si>
   <si>
     <t xml:space="preserve">Every input in this model, where it comes from, and how current it is. Click "Open ↗" for the underlying source. Refresh stamps also appear on Market Inputs; refreshes are logged in Version History.</t>
@@ -1260,7 +1269,7 @@
     <t xml:space="preserve">Palantir Q4 FY2025 earnings release, 8-K Ex. 99.1, filed Feb 2, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Static actuals — restate on next annual filing</t>
+    <t xml:space="preserve">Static actuals · restate on next annual filing</t>
   </si>
   <si>
     <t xml:space="preserve">FY2023 financial statements</t>
@@ -1281,7 +1290,7 @@
     <t xml:space="preserve">FY2025 Form 10-K, segment &amp; geographic note, filed Feb 17, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Static — Europe/APAC allocation of non-US revenue is an estimate</t>
+    <t xml:space="preserve">Static · Europe/APAC allocation of non-US revenue is an estimate</t>
   </si>
   <si>
     <t xml:space="preserve">Customer counts &amp; government/commercial splits</t>
@@ -1293,7 +1302,7 @@
     <t xml:space="preserve">Q4 2025 investor presentation (954 total / 780 commercial customers)</t>
   </si>
   <si>
-    <t xml:space="preserve">Static — update quarterly</t>
+    <t xml:space="preserve">Static · update quarterly</t>
   </si>
   <si>
     <t xml:space="preserve">GUIDANCE &amp; BUDGET</t>
@@ -1308,7 +1317,7 @@
     <t xml:space="preserve">Issued with Q4 FY2024 release, Feb 3, 2025 ($3,741–3,757M revenue)</t>
   </si>
   <si>
-    <t xml:space="preserve">Static — replace with FY2026 guidance next cycle</t>
+    <t xml:space="preserve">Static · replace with FY2026 guidance next cycle</t>
   </si>
   <si>
     <t xml:space="preserve">MARKET DATA</t>
@@ -1344,7 +1353,7 @@
     <t xml:space="preserve">Market Inputs · Competitor Benchmarking</t>
   </si>
   <si>
-    <t xml:space="preserve">stockanalysis.com (PLTR) — data: S&amp;P Global Market Intelligence, close Jul 17, 2026</t>
+    <t xml:space="preserve">stockanalysis.com (PLTR); data: S&amp;P Global Market Intelligence, close Jul 17, 2026</t>
   </si>
   <si>
     <t xml:space="preserve">refresh_market_data.py scales by live price ratio</t>
@@ -1353,7 +1362,7 @@
     <t xml:space="preserve">VALUATION &amp; INDUSTRY BENCHMARKS</t>
   </si>
   <si>
-    <t xml:space="preserve">Comp fundamentals — Snowflake (FY ended 1/26)</t>
+    <t xml:space="preserve">Comp fundamentals · Snowflake (FY ended 1/26)</t>
   </si>
   <si>
     <t xml:space="preserve">Competitor Benchmarking</t>
@@ -1362,10 +1371,10 @@
     <t xml:space="preserve">Snowflake Q4 FY2026 earnings release, 8-K, Feb 25, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Static — update after comp earnings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comp fundamentals — Datadog (FY2025)</t>
+    <t xml:space="preserve">Static · update after comp earnings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comp fundamentals · Datadog (FY2025)</t>
   </si>
   <si>
     <t xml:space="preserve">Datadog Q4/FY2025 results, Feb 10, 2026</t>
@@ -1380,7 +1389,7 @@
     <t xml:space="preserve">2026-07-10</t>
   </si>
   <si>
-    <t xml:space="preserve">Manual — ask Claude to refresh</t>
+    <t xml:space="preserve">Manual · ask Claude to refresh</t>
   </si>
   <si>
     <t xml:space="preserve">FORECAST ASSUMPTIONS</t>
@@ -1398,7 +1407,7 @@
     <t xml:space="preserve">Every change is logged on the Version History tab</t>
   </si>
   <si>
-    <t xml:space="preserve">Conventions: "Static actuals" never change once filed (restated only if the company restates). Market data carries dual stamps — "Data as of" (the market close the values describe) and "Last refreshed" (when the file was last updated). Analyst assumptions are the author's judgment; the Version History tab is the audit trail.</t>
+    <t xml:space="preserve">Conventions: "Static actuals" never change once filed (restated only if the company restates). Market data carries dual stamps; "Data as of" (the market close the values describe) and "Last refreshed" (when the file was last updated). Analyst assumptions are the author's judgment; the Version History tab is the audit trail.</t>
   </si>
 </sst>
 </file>
@@ -1943,7 +1952,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2296,20 +2305,20 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="str">
-        <f aca="false">HYPERLINK("Finance_AI_Dashboard.html","▸  Interactive dashboard  —  toggle industry, scenario and region in your browser (same folder)")</f>
-        <v>▸  Interactive dashboard  —  toggle industry, scenario and region in your browser (same folder)</v>
+        <f aca="false">HYPERLINK("Finance_AI_Dashboard.html","▸  Interactive dashboard  ·  toggle industry, scenario and region in your browser (same folder)")</f>
+        <v>▸  Interactive dashboard  ·  toggle industry, scenario and region in your browser (same folder)</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="str">
-        <f aca="false">HYPERLINK("README.md","▸  Portfolio README  —  overview of all three models and how they fit together")</f>
-        <v>▸  Portfolio README  —  overview of all three models and how they fit together</v>
+        <f aca="false">HYPERLINK("README.md","▸  Portfolio README  ·  overview of all three models and how they fit together")</f>
+        <v>▸  Portfolio README  ·  overview of all three models and how they fit together</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="str">
-        <f aca="false">HYPERLINK("refresh_market_data.py","▸  Market-data refresh script  —  run to update prices, rates and refresh stamps everywhere")</f>
-        <v>▸  Market-data refresh script  —  run to update prices, rates and refresh stamps everywhere</v>
+        <f aca="false">HYPERLINK("refresh_market_data.py","▸  Market-data refresh script  ·  run to update prices, rates and refresh stamps everywhere")</f>
+        <v>▸  Market-data refresh script  ·  run to update prices, rates and refresh stamps everywhere</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2319,68 +2328,68 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Assumptions'!A1","▸  Assumptions  —  Margin, tax, working-capital and financing drivers")</f>
-        <v>▸  Assumptions  —  Margin, tax, working-capital and financing drivers</v>
+        <f aca="false">HYPERLINK("#'Assumptions'!A1","▸  Assumptions  ·  Margin, tax, working-capital and financing drivers")</f>
+        <v>▸  Assumptions  ·  Margin, tax, working-capital and financing drivers</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Revenue Drivers'!A1","▸  Revenue Drivers  —  Bottoms-up sector build driving revenue and key costs")</f>
-        <v>▸  Revenue Drivers  —  Bottoms-up sector build driving revenue and key costs</v>
+        <f aca="false">HYPERLINK("#'Revenue Drivers'!A1","▸  Revenue Drivers  ·  Bottoms-up sector build driving revenue and key costs")</f>
+        <v>▸  Revenue Drivers  ·  Bottoms-up sector build driving revenue and key costs</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Regional Breakdown'!A1","▸  Regional Breakdown  —  NA / Europe / APAC splits and the Standard / Best / Low case selector")</f>
-        <v>▸  Regional Breakdown  —  NA / Europe / APAC splits and the Standard / Best / Low case selector</v>
+        <f aca="false">HYPERLINK("#'Regional Breakdown'!A1","▸  Regional Breakdown  ·  NA / Europe / APAC splits and the Standard / Best / Low case selector")</f>
+        <v>▸  Regional Breakdown  ·  NA / Europe / APAC splits and the Standard / Best / Low case selector</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Income Statement'!A1","▸  Income Statement  —  Revenue build-down to EPS")</f>
-        <v>▸  Income Statement  —  Revenue build-down to EPS</v>
+        <f aca="false">HYPERLINK("#'Income Statement'!A1","▸  Income Statement  ·  Revenue build-down to EPS")</f>
+        <v>▸  Income Statement  ·  Revenue build-down to EPS</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Balance Sheet'!A1","▸  Balance Sheet  —  Assets, liabilities and equity, with balance check")</f>
-        <v>▸  Balance Sheet  —  Assets, liabilities and equity, with balance check</v>
+        <f aca="false">HYPERLINK("#'Balance Sheet'!A1","▸  Balance Sheet  ·  Assets, liabilities and equity, with balance check")</f>
+        <v>▸  Balance Sheet  ·  Assets, liabilities and equity, with balance check</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Cash Flow'!A1","▸  Cash Flow  —  Indirect-method cash flow; ending cash links to the balance sheet")</f>
-        <v>▸  Cash Flow  —  Indirect-method cash flow; ending cash links to the balance sheet</v>
+        <f aca="false">HYPERLINK("#'Cash Flow'!A1","▸  Cash Flow  ·  Indirect-method cash flow; ending cash links to the balance sheet")</f>
+        <v>▸  Cash Flow  ·  Indirect-method cash flow; ending cash links to the balance sheet</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Budget vs Actual'!A1","▸  Budget vs Actual  —  FY2025 vs guidance with automatic &gt;10% variance flagging")</f>
-        <v>▸  Budget vs Actual  —  FY2025 vs guidance with automatic &gt;10% variance flagging</v>
+        <f aca="false">HYPERLINK("#'Budget vs Actual'!A1","▸  Budget vs Actual  ·  FY2025 vs guidance with automatic &gt;10% variance flagging")</f>
+        <v>▸  Budget vs Actual  ·  FY2025 vs guidance with automatic &gt;10% variance flagging</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Market Inputs'!A1","▸  Market Inputs  —  Rates and valuation multiples with refresh stamps")</f>
-        <v>▸  Market Inputs  —  Rates and valuation multiples with refresh stamps</v>
+        <f aca="false">HYPERLINK("#'Market Inputs'!A1","▸  Market Inputs  ·  Rates and valuation multiples with refresh stamps")</f>
+        <v>▸  Market Inputs  ·  Rates and valuation multiples with refresh stamps</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Competitor Benchmarking'!A1","▸  Competitor Benchmarking  —  Two public comps + peer median + industry benchmarks")</f>
-        <v>▸  Competitor Benchmarking  —  Two public comps + peer median + industry benchmarks</v>
+        <f aca="false">HYPERLINK("#'Competitor Benchmarking'!A1","▸  Competitor Benchmarking  ·  Two public comps + peer median + industry benchmarks")</f>
+        <v>▸  Competitor Benchmarking  ·  Two public comps + peer median + industry benchmarks</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Version History'!A1","▸  Version History  —  Audit log of every assumptions and data refresh")</f>
-        <v>▸  Version History  —  Audit log of every assumptions and data refresh</v>
+        <f aca="false">HYPERLINK("#'Version History'!A1","▸  Version History  ·  Audit log of every assumptions and data refresh")</f>
+        <v>▸  Version History  ·  Audit log of every assumptions and data refresh</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Sources'!A1","▸  Sources  —  Where every input comes from — citations, links, last-updated dates")</f>
-        <v>▸  Sources  —  Where every input comes from — citations, links, last-updated dates</v>
+        <f aca="false">HYPERLINK("#'Sources'!A1","▸  Sources  ·  Where every input comes from: citations, links, last-updated dates")</f>
+        <v>▸  Sources  ·  Where every input comes from: citations, links, last-updated dates</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2990,16 +2999,26 @@
         <v>395</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="67"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="64" t="s">
+        <v>396</v>
+      </c>
+      <c r="B14" s="64" t="s">
+        <v>372</v>
+      </c>
+      <c r="C14" s="64" t="s">
+        <v>368</v>
+      </c>
+      <c r="D14" s="67" t="s">
+        <v>397</v>
+      </c>
+      <c r="E14" s="67" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -3032,37 +3051,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="68" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B4" s="68" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C4" s="68" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D4" s="68" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E4" s="68" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F4" s="68" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="69" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -3072,13 +3091,13 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="65" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B6" s="65" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D6" s="71" t="str">
         <f aca="false">HYPERLINK("https://www.sec.gov/Archives/edgar/data/1321655/000132165526000004/a2025q4ex991earningsrelease.htm","Open ↗")</f>
@@ -3088,18 +3107,18 @@
         <v>367</v>
       </c>
       <c r="F6" s="72" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="65" t="s">
+        <v>413</v>
+      </c>
+      <c r="B7" s="65" t="s">
         <v>410</v>
       </c>
-      <c r="B7" s="65" t="s">
-        <v>407</v>
-      </c>
       <c r="C7" s="65" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D7" s="71" t="str">
         <f aca="false">HYPERLINK("https://www.sec.gov/Archives/edgar/data/1321655/000132165525000007/a2024q4ex991earningsrelease.htm","Open ↗")</f>
@@ -3109,18 +3128,18 @@
         <v>367</v>
       </c>
       <c r="F7" s="72" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="65" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D8" s="71" t="str">
         <f aca="false">HYPERLINK("https://www.sec.gov/Archives/edgar/data/1321655/000132165526000011/R70.htm","Open ↗")</f>
@@ -3130,18 +3149,18 @@
         <v>372</v>
       </c>
       <c r="F8" s="72" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="65" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B9" s="65" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C9" s="65" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D9" s="71" t="str">
         <f aca="false">HYPERLINK("https://investors.palantir.com/files/Palantir%20-%20Q4%202025%20Investor%20Presentation.pdf","Open ↗")</f>
@@ -3151,12 +3170,12 @@
         <v>372</v>
       </c>
       <c r="F9" s="72" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="69" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B10" s="70"/>
       <c r="C10" s="70"/>
@@ -3166,13 +3185,13 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="65" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B11" s="65" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C11" s="65" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D11" s="71" t="str">
         <f aca="false">HYPERLINK("https://www.sec.gov/Archives/edgar/data/1321655/000132165525000007/a2024q4ex991earningsrelease.htm","Open ↗")</f>
@@ -3182,12 +3201,12 @@
         <v>372</v>
       </c>
       <c r="F11" s="72" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="69" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B12" s="70"/>
       <c r="C12" s="70"/>
@@ -3197,70 +3216,70 @@
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="65" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B13" s="65" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C13" s="65" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D13" s="71" t="str">
         <f aca="false">HYPERLINK("https://home.treasury.gov/resource-center/data-chart-center/interest-rates/","Open ↗")</f>
         <v>Open ↗</v>
       </c>
       <c r="E13" s="65" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F13" s="72" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="65" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B14" s="65" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C14" s="65" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D14" s="71" t="str">
         <f aca="false">HYPERLINK("https://www.newyorkfed.org/markets/reference-rates/sofr","Open ↗")</f>
         <v>Open ↗</v>
       </c>
       <c r="E14" s="65" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F14" s="72" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="65" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B15" s="65" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C15" s="65" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D15" s="71" t="str">
         <f aca="false">HYPERLINK("https://stockanalysis.com/stocks/pltr/statistics/","Open ↗")</f>
         <v>Open ↗</v>
       </c>
       <c r="E15" s="65" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F15" s="72" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="69" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B16" s="70"/>
       <c r="C16" s="70"/>
@@ -3270,13 +3289,13 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="65" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B17" s="65" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C17" s="65" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D17" s="71" t="str">
         <f aca="false">HYPERLINK("https://www.sec.gov/Archives/edgar/data/1640147/000162828026011631/fy2026q4earnings.htm","Open ↗")</f>
@@ -3286,18 +3305,18 @@
         <v>372</v>
       </c>
       <c r="F17" s="72" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="65" t="s">
+        <v>447</v>
+      </c>
+      <c r="B18" s="65" t="s">
         <v>444</v>
       </c>
-      <c r="B18" s="65" t="s">
-        <v>441</v>
-      </c>
       <c r="C18" s="65" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D18" s="71" t="str">
         <f aca="false">HYPERLINK("https://investors.datadoghq.com/news-releases/news-release-details/datadog-announces-fourth-quarter-and-fiscal-year-2025-financial/","Open ↗")</f>
@@ -3307,33 +3326,33 @@
         <v>372</v>
       </c>
       <c r="F18" s="72" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="65" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B19" s="65" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C19" s="65" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D19" s="71" t="str">
         <f aca="false">HYPERLINK("https://cloudedjudgement.substack.com/p/clouded-judgement-71026-own-your","Open ↗")</f>
         <v>Open ↗</v>
       </c>
       <c r="E19" s="65" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F19" s="72" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="69" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B20" s="70"/>
       <c r="C20" s="70"/>
@@ -3343,13 +3362,13 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="65" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B21" s="65" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C21" s="65" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D21" s="73" t="s">
         <v>331</v>
@@ -3358,12 +3377,12 @@
         <v>372</v>
       </c>
       <c r="F21" s="72" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
